--- a/mock数据/JD2项目_test-boq/早期介入/交付预案/输出结果/验收策略.xlsx
+++ b/mock数据/JD2项目_test-boq/早期介入/交付预案/输出结果/验收策略.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,40 +471,220 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>硬件设备</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>POD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>硬件到货</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>硬件到货</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>硬件设备接收文档</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>到货</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>设备到货清点</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>型号/数量与 BOQ 一致</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>到货签收</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>到货验收单</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>到货</t>
-        </is>
-      </c>
       <c r="I2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>软件部分</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>License激活完成软件验收</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>License加载完成</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>License加载</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>License加载证明</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>License加载</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>服务部分</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>对应服务条目交付完成</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>对应服务条目交付完成</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>完工验/PAC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>完工验/PAC报告</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>安装 PAC</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>培训服务</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>培训课程完成即验收</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>培训课程完成</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>培训完成</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>签到表</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>培训完成</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>维保服务</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>硬件到货和License激活后30天</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OM起算</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>直线法</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>月度</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>1</v>
       </c>
     </row>
